--- a/7rmartsupermarket/src/test/resources/TestDataSample.xlsx
+++ b/7rmartsupermarket/src/test/resources/TestDataSample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f51d8c6d06a5be2/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{1D157668-13F1-465B-BD30-9B7B661FB2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E73E9D1-CBF9-4841-874C-8CE026C9F28A}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{1D157668-13F1-465B-BD30-9B7B661FB2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E82008C-F6C1-491F-9683-F1E88B0E9054}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{33C81A63-3368-4B08-8F50-38682D612412}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{33C81A63-3368-4B08-8F50-38682D612412}"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="locations" sheetId="3" r:id="rId3"/>
     <sheet name="deliveryboydetails" sheetId="4" r:id="rId4"/>
     <sheet name="categoryname" sheetId="5" r:id="rId5"/>
+    <sheet name="News" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>Username</t>
   </si>
@@ -131,6 +132,12 @@
   </si>
   <si>
     <t>Fruit</t>
+  </si>
+  <si>
+    <t>News</t>
+  </si>
+  <si>
+    <t>New Products are Now Avaliable</t>
   </si>
 </sst>
 </file>
@@ -738,4 +745,27 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FAD1B4-BD7E-436C-8B36-01772062E2BB}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/7rmartsupermarket/src/test/resources/TestDataSample.xlsx
+++ b/7rmartsupermarket/src/test/resources/TestDataSample.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f51d8c6d06a5be2/Documents/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{1D157668-13F1-465B-BD30-9B7B661FB2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E82008C-F6C1-491F-9683-F1E88B0E9054}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{A34F82EE-5B29-4573-B923-B0706CC2C33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{33C81A63-3368-4B08-8F50-38682D612412}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{33C81A63-3368-4B08-8F50-38682D612412}"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
@@ -20,7 +15,8 @@
     <sheet name="categoryname" sheetId="5" r:id="rId5"/>
     <sheet name="News" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:Q15"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -210,10 +206,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
